--- a/dcf/SE.xlsx
+++ b/dcf/SE.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.09794284713205308</v>
+        <v>0.09795929711622382</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.1029428471320531</v>
+        <v>0.1029592971162238</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.1079428471320531</v>
+        <v>0.1079592971162238</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.1129428471320531</v>
+        <v>0.1129592971162238</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.1179428471320531</v>
+        <v>0.1179592971162238</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1229428471320531</v>
+        <v>0.1229592971162238</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1279428471320531</v>
+        <v>0.1279592971162238</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>96.75438660090526</v>
+        <v>85.41866225221339</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>93.5893156995123</v>
+        <v>82.72918369468654</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>90.57058792057283</v>
+        <v>80.16370924461252</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>87.69071492772068</v>
+        <v>77.71590336237557</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>84.94262589975577</v>
+        <v>75.37978342815055</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>82.31964241940049</v>
+        <v>73.14969852798534</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>79.81545497942328</v>
+        <v>71.02030960570147</v>
       </c>
     </row>
     <row r="6">
@@ -1151,103 +1151,103 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>102.6475464365945</v>
+        <v>90.38933516565878</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>99.22070397413117</v>
+        <v>87.47906473544667</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>95.95293843862058</v>
+        <v>84.7035386154548</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>92.83608873422786</v>
+        <v>82.05585384189591</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>89.86244961651698</v>
+        <v>79.5294927041592</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>87.02474423893142</v>
+        <v>77.11829955540861</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>84.31609846930445</v>
+        <v>74.81645911775368</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="n">
         <v>11</v>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>108.5407062722837</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>104.85209224875</v>
+      <c r="B7" s="53" t="n">
+        <v>95.36000807910416</v>
+      </c>
+      <c r="C7" s="53" t="n">
+        <v>92.22894577620679</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>101.3352889566683</v>
+        <v>89.24336798629709</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>97.98146254073504</v>
+        <v>86.39580432141625</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>94.7822733332782</v>
+        <v>83.67920198016785</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>91.72984605846236</v>
+        <v>81.08690058283189</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>88.81674195918561</v>
+        <v>78.61260862980589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n">
         <v>12</v>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>114.4338661079729</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>110.4834805233689</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>106.7176394747161</v>
+      <c r="B8" s="53" t="n">
+        <v>100.3306809925495</v>
+      </c>
+      <c r="C8" s="53" t="n">
+        <v>96.97882681696689</v>
+      </c>
+      <c r="D8" s="53" t="n">
+        <v>93.78319735713936</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>103.1268363472422</v>
+        <v>90.73575480093659</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>99.70209705003943</v>
+        <v>87.82891125617651</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>96.4349478779933</v>
+        <v>85.05550161025516</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>93.31738544906678</v>
+        <v>82.4087581418581</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
         <v>13</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>120.3270259436622</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>116.1148687979878</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>112.0999899927638</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>108.2722101537494</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>104.6219207668007</v>
+      <c r="B9" s="53" t="n">
+        <v>105.3013539059949</v>
+      </c>
+      <c r="C9" s="53" t="n">
+        <v>101.728707857727</v>
+      </c>
+      <c r="D9" s="53" t="n">
+        <v>98.32302672798164</v>
+      </c>
+      <c r="E9" s="53" t="n">
+        <v>95.07570528045694</v>
+      </c>
+      <c r="F9" s="53" t="n">
+        <v>91.97862053218516</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>101.1400496975242</v>
+        <v>89.02410263767844</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>97.81802893894795</v>
+        <v>86.2049076539103</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>126.2201857793514</v>
+        <v>110.2720268194403</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>121.7462570726066</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>117.4823405108116</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>113.4175839602566</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>109.5417444835619</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>105.8451515170552</v>
+        <v>106.4785888984871</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>102.8628560988239</v>
+      </c>
+      <c r="E10" s="53" t="n">
+        <v>99.41565575997727</v>
+      </c>
+      <c r="F10" s="53" t="n">
+        <v>96.12832980819381</v>
+      </c>
+      <c r="G10" s="53" t="n">
+        <v>92.9927036651017</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>102.3186724288291</v>
+        <v>90.00105716596251</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>132.1133456150406</v>
+        <v>115.2426997328857</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>127.3776453472255</v>
+        <v>111.2284699392472</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>122.8646910288593</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>118.5629577667638</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>114.4615682003231</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>110.5502533365861</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>106.8193159187103</v>
+        <v>107.4026854696662</v>
+      </c>
+      <c r="E11" s="53" t="n">
+        <v>103.7556062394976</v>
+      </c>
+      <c r="F11" s="53" t="n">
+        <v>100.2780390842025</v>
+      </c>
+      <c r="G11" s="53" t="n">
+        <v>96.96130469252496</v>
+      </c>
+      <c r="H11" s="53" t="n">
+        <v>93.79720667801472</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>103.3000030517578</v>
+        <v>105.379997253418</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.1129428471320531</v>
+        <v>0.1129592971162238</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9561866022756598</v>
+        <v>0.9566730034679615</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>103.3000030517578</v>
+        <v>105.379997253418</v>
       </c>
     </row>
     <row r="49">
@@ -24414,7 +24414,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>103.1268363472422</v>
+        <v>90.73575480093659</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>149.0815932648419</v>
+        <v>127.5524486251493</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>70.31220976964968</v>
+        <v>63.67060891579119</v>
       </c>
     </row>
     <row r="59">
